--- a/rabbit-web-app/public/sample_excels/dispatch/shipper_single_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/shipper_single_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Shipper" sheetId="1" r:id="rId1"/>
+    <sheet name="Shippers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,15 +407,18 @@
         <v>address</v>
       </c>
       <c r="C1" t="str">
+        <v>email</v>
+      </c>
+      <c r="D1" t="str">
         <v>phone</v>
       </c>
-      <c r="D1" t="str">
-        <v>pinCode</v>
-      </c>
       <c r="E1" t="str">
+        <v>zipCode</v>
+      </c>
+      <c r="F1" t="str">
         <v>startTime</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>endTime</v>
       </c>
     </row>
@@ -435,21 +430,24 @@
         <v>Plot No. 45, Sector 18, Vashi, Navi Mumbai, Maharashtra</v>
       </c>
       <c r="C2" t="str">
-        <v>+91 98201 12345</v>
+        <v>vashi.hub@relianceretail.com</v>
       </c>
       <c r="D2" t="str">
+        <v>98201 12345</v>
+      </c>
+      <c r="E2" t="str">
         <v>400703</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>08:00 AM</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>06:00 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>